--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mail.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mail.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -495,12 +500,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>您在交易行竞拍的</t>
+      <t>您在藏宝阁竞拍的</t>
     </r>
     <r>
       <rPr>
@@ -530,11 +530,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>很遗憾，您没能竞拍到</t>
     </r>
     <r>
@@ -606,13 +601,65 @@
     <t>竞拍失败#被下架</t>
   </si>
   <si>
-    <t>您在交易行竞拍的&lt;color=#9b39cc&gt;%s&lt;/color&gt;已被下架，%s退还。</t>
+    <r>
+      <t>您在藏宝阁竞拍的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已被下架，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退还。</t>
+    </r>
   </si>
   <si>
     <t>106004</t>
   </si>
   <si>
-    <t>您在交易行成功购买了&lt;color=#9b39cc&gt;%s&lt;/color&gt;，请查收。</t>
+    <r>
+      <t>您在藏宝阁成功购买了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，请查收。</t>
+    </r>
   </si>
   <si>
     <t>106005</t>
@@ -621,7 +668,25 @@
     <t>预购成功</t>
   </si>
   <si>
-    <t>您在交易行成功预购了&lt;color=#9b39cc&gt;%s&lt;/color&gt;，请查收。</t>
+    <r>
+      <t>您在藏宝阁成功预购了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，请查收。</t>
+    </r>
   </si>
   <si>
     <t>106006</t>
@@ -639,7 +704,41 @@
     <t>预购失败#被下架</t>
   </si>
   <si>
-    <t>您在交易行预购的&lt;color=#9b39cc&gt;%s&lt;/color&gt;被卖家下架，%s退还。</t>
+    <r>
+      <t>您在藏宝阁预购的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>被卖家下架，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>%s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退还。</t>
+    </r>
   </si>
   <si>
     <t>106009</t>
@@ -648,7 +747,25 @@
     <t>上架超时</t>
   </si>
   <si>
-    <t>您在交易行上架的&lt;color=#9b39cc&gt;%s&lt;/color&gt;已超时，请重新上架。</t>
+    <r>
+      <t>您在藏宝阁上架的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已超时，请重新上架。</t>
+    </r>
   </si>
   <si>
     <t>106010</t>
@@ -657,7 +774,25 @@
     <t>上架失败</t>
   </si>
   <si>
-    <t>您在交易行上架的&lt;color=#9b39cc&gt;%s&lt;/color&gt;未能成功上架，请重新上架。</t>
+    <r>
+      <t>您在藏宝阁上架的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未能成功上架，请重新上架。</t>
+    </r>
   </si>
   <si>
     <t>106011</t>
@@ -666,7 +801,25 @@
     <t>成功售出</t>
   </si>
   <si>
-    <t>您在交易行成功售出&lt;color=#9b39cc&gt;%s&lt;/color&gt;。</t>
+    <r>
+      <t>您在藏宝阁成功售出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
   </si>
   <si>
     <t>战盟拍卖分红</t>
@@ -746,7 +899,7 @@
     <t>商品下架</t>
   </si>
   <si>
-    <t>您在交易行下架的商品已寄回，请查收</t>
+    <t>您在藏宝阁下架的商品已寄回，请查收</t>
   </si>
   <si>
     <t>107001</t>
@@ -758,7 +911,7 @@
     <t>成功创建战盟</t>
   </si>
   <si>
-    <t>恭喜您成功创建了战盟，盟主大人！</t>
+    <t>恭喜您成功创建了战盟！</t>
   </si>
   <si>
     <t>107002</t>
@@ -770,7 +923,17 @@
     <t>同意入会</t>
   </si>
   <si>
-    <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;同意您加入。</t>
+    <r>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同意您加入。</t>
+    </r>
   </si>
   <si>
     <t>107003</t>
@@ -782,7 +945,17 @@
     <t>拒绝入会</t>
   </si>
   <si>
-    <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;拒绝了您的申请。</t>
+    <r>
+      <t>&lt;color=#9b39cc&gt;%s&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拒绝了您的加入。</t>
+    </r>
   </si>
   <si>
     <t>107004</t>
@@ -818,7 +991,7 @@
     <t>退出战盟</t>
   </si>
   <si>
-    <t>您已经退出了战盟。</t>
+    <t>您已经退出战盟。</t>
   </si>
   <si>
     <t>108001</t>
@@ -1353,13 +1526,13 @@
     <t>弹劾成功</t>
   </si>
   <si>
-    <t>弹劾成功，%s已经不是战盟盟主，当前战盟处于无盟主状态。</t>
+    <t>弹劾成功，%s已不是盟主，当前战盟处于无盟主状态。</t>
   </si>
   <si>
     <t>弹劾失败</t>
   </si>
   <si>
-    <t>弹劾失败，%s依然是战盟盟主。</t>
+    <t>弹劾失败，%s依然是盟主。</t>
   </si>
   <si>
     <t>战盟任务奖励补发</t>
@@ -1380,7 +1553,7 @@
     <t>有盟友发起了竞选！</t>
   </si>
   <si>
-    <t>盟主之位空置已久，现在有盟友对盟主之位发起了竞选投票，可在战盟竞选页面进行投票，投票结果将在24小时后进行结算。</t>
+    <t>盟主之位空置中，现在有盟友对盟主之位发起竞选投票，可在战盟竞选页面进行投票，结果将在24小时后进行结算。</t>
   </si>
   <si>
     <t>发起弹劾</t>
@@ -1389,7 +1562,7 @@
     <t>有盟友发起了弹劾！</t>
   </si>
   <si>
-    <t>您的战盟中有人对盟主%s发起了弹劾，弹劾投票已经开启，可在战盟弹劾页面进行投票，投票结果将在24小时后进行结算。</t>
+    <t>您的战盟中有人对盟主%s发起了弹劾，弹劾投票已开启，可在战盟弹劾页面进行投票，结果将在24小时后进行结算。</t>
   </si>
   <si>
     <t>发起取代</t>
@@ -1398,7 +1571,7 @@
     <t>有盟友发起了取代！</t>
   </si>
   <si>
-    <t>您的战盟中有人对盟主%s发起了取代，取代投票已经开启，可在战盟取代页面进行投票，投票结果将在24小时后进行结算。</t>
+    <t>您的战盟中有人对盟主%s发起了取代，取代投票已经开启，可在战盟取代页面进行投票，结果将在24小时后进行结算。</t>
   </si>
   <si>
     <t>取代失败</t>
@@ -3369,7 +3542,7 @@
       <c r="D20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="9" t="s">
         <v>76</v>
       </c>
       <c r="F20" s="9">
@@ -3392,7 +3565,7 @@
       <c r="D21" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="9" t="s">
         <v>78</v>
       </c>
       <c r="F21" s="9">
@@ -3415,7 +3588,7 @@
       <c r="D22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="9" t="s">
         <v>81</v>
       </c>
       <c r="F22" s="9">
@@ -3461,7 +3634,7 @@
       <c r="D24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="9" t="s">
         <v>87</v>
       </c>
       <c r="F24" s="9">
@@ -3484,7 +3657,7 @@
       <c r="D25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="9" t="s">
         <v>90</v>
       </c>
       <c r="F25" s="9">
@@ -3507,7 +3680,7 @@
       <c r="D26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="9" t="s">
         <v>93</v>
       </c>
       <c r="F26" s="9">
@@ -3530,7 +3703,7 @@
       <c r="D27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="9" t="s">
         <v>96</v>
       </c>
       <c r="F27" s="9">
@@ -3597,7 +3770,7 @@
       <c r="D30" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="9" t="s">
         <v>106</v>
       </c>
       <c r="F30" s="9">
@@ -3712,7 +3885,7 @@
       <c r="D35" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="9" t="s">
         <v>126</v>
       </c>
       <c r="F35" s="9">
